--- a/data_input/source_data/Program_heli.xlsx
+++ b/data_input/source_data/Program_heli.xlsx
@@ -1296,11 +1296,11 @@
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
+      <c r="P5" s="7">
+        <v>7</v>
+      </c>
       <c r="Q5" s="7"/>
-      <c r="R5" s="7">
-        <v>2</v>
-      </c>
+      <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>

--- a/data_input/source_data/Program_heli.xlsx
+++ b/data_input/source_data/Program_heli.xlsx
@@ -118,7 +118,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,12 +140,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -188,19 +182,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -548,25 +536,25 @@
       <c r="G1" s="3">
         <v>5</v>
       </c>
-      <c r="H1" s="4">
+      <c r="H1" s="3">
         <v>6</v>
       </c>
-      <c r="I1" s="5">
+      <c r="I1" s="3">
         <v>7</v>
       </c>
-      <c r="J1" s="5">
+      <c r="J1" s="3">
         <v>8</v>
       </c>
-      <c r="K1" s="5">
+      <c r="K1" s="3">
         <v>9</v>
       </c>
-      <c r="L1" s="5">
+      <c r="L1" s="3">
         <v>10</v>
       </c>
-      <c r="M1" s="5">
+      <c r="M1" s="3">
         <v>11</v>
       </c>
-      <c r="N1" s="5">
+      <c r="N1" s="3">
         <v>12</v>
       </c>
       <c r="O1" s="3">
@@ -584,25 +572,25 @@
       <c r="S1" s="3">
         <v>5</v>
       </c>
-      <c r="T1" s="4">
+      <c r="T1" s="3">
         <v>6</v>
       </c>
-      <c r="U1" s="5">
+      <c r="U1" s="3">
         <v>7</v>
       </c>
-      <c r="V1" s="5">
+      <c r="V1" s="3">
         <v>8</v>
       </c>
-      <c r="W1" s="5">
+      <c r="W1" s="3">
         <v>9</v>
       </c>
-      <c r="X1" s="5">
+      <c r="X1" s="3">
         <v>10</v>
       </c>
-      <c r="Y1" s="5">
+      <c r="Y1" s="3">
         <v>11</v>
       </c>
-      <c r="Z1" s="5">
+      <c r="Z1" s="3">
         <v>12</v>
       </c>
       <c r="AA1" s="3">
@@ -620,25 +608,25 @@
       <c r="AE1" s="3">
         <v>5</v>
       </c>
-      <c r="AF1" s="4">
+      <c r="AF1" s="3">
         <v>6</v>
       </c>
-      <c r="AG1" s="5">
+      <c r="AG1" s="3">
         <v>7</v>
       </c>
-      <c r="AH1" s="5">
+      <c r="AH1" s="3">
         <v>8</v>
       </c>
-      <c r="AI1" s="5">
+      <c r="AI1" s="3">
         <v>9</v>
       </c>
-      <c r="AJ1" s="5">
+      <c r="AJ1" s="3">
         <v>10</v>
       </c>
-      <c r="AK1" s="5">
+      <c r="AK1" s="3">
         <v>11</v>
       </c>
-      <c r="AL1" s="5">
+      <c r="AL1" s="3">
         <v>12</v>
       </c>
       <c r="AM1" s="3">
@@ -656,25 +644,25 @@
       <c r="AQ1" s="3">
         <v>5</v>
       </c>
-      <c r="AR1" s="4">
+      <c r="AR1" s="3">
         <v>6</v>
       </c>
-      <c r="AS1" s="5">
+      <c r="AS1" s="3">
         <v>7</v>
       </c>
-      <c r="AT1" s="5">
+      <c r="AT1" s="3">
         <v>8</v>
       </c>
-      <c r="AU1" s="5">
+      <c r="AU1" s="3">
         <v>9</v>
       </c>
-      <c r="AV1" s="5">
+      <c r="AV1" s="3">
         <v>10</v>
       </c>
-      <c r="AW1" s="5">
+      <c r="AW1" s="3">
         <v>11</v>
       </c>
-      <c r="AX1" s="5">
+      <c r="AX1" s="3">
         <v>12</v>
       </c>
       <c r="AY1" s="3">
@@ -692,25 +680,25 @@
       <c r="BC1" s="3">
         <v>5</v>
       </c>
-      <c r="BD1" s="4">
+      <c r="BD1" s="3">
         <v>6</v>
       </c>
-      <c r="BE1" s="5">
+      <c r="BE1" s="3">
         <v>7</v>
       </c>
-      <c r="BF1" s="5">
+      <c r="BF1" s="3">
         <v>8</v>
       </c>
-      <c r="BG1" s="5">
+      <c r="BG1" s="3">
         <v>9</v>
       </c>
-      <c r="BH1" s="5">
+      <c r="BH1" s="3">
         <v>10</v>
       </c>
-      <c r="BI1" s="5">
+      <c r="BI1" s="3">
         <v>11</v>
       </c>
-      <c r="BJ1" s="5">
+      <c r="BJ1" s="3">
         <v>12</v>
       </c>
     </row>
@@ -755,596 +743,596 @@
       <c r="N2" s="3">
         <v>2025</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="6">
         <v>2026</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="6">
         <v>2026</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="6">
         <v>2026</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="6">
         <v>2026</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="6">
         <v>2026</v>
       </c>
-      <c r="T2" s="8">
+      <c r="T2" s="6">
         <v>2026</v>
       </c>
-      <c r="U2" s="8">
+      <c r="U2" s="6">
         <v>2026</v>
       </c>
-      <c r="V2" s="8">
+      <c r="V2" s="6">
         <v>2026</v>
       </c>
-      <c r="W2" s="8">
+      <c r="W2" s="6">
         <v>2026</v>
       </c>
-      <c r="X2" s="8">
+      <c r="X2" s="6">
         <v>2026</v>
       </c>
-      <c r="Y2" s="8">
+      <c r="Y2" s="6">
         <v>2026</v>
       </c>
-      <c r="Z2" s="8">
+      <c r="Z2" s="6">
         <v>2026</v>
       </c>
-      <c r="AA2" s="8">
+      <c r="AA2" s="6">
         <v>2027</v>
       </c>
-      <c r="AB2" s="8">
+      <c r="AB2" s="6">
         <v>2027</v>
       </c>
-      <c r="AC2" s="8">
+      <c r="AC2" s="6">
         <v>2027</v>
       </c>
-      <c r="AD2" s="8">
+      <c r="AD2" s="6">
         <v>2027</v>
       </c>
-      <c r="AE2" s="8">
+      <c r="AE2" s="6">
         <v>2027</v>
       </c>
-      <c r="AF2" s="8">
+      <c r="AF2" s="6">
         <v>2027</v>
       </c>
-      <c r="AG2" s="8">
+      <c r="AG2" s="6">
         <v>2027</v>
       </c>
-      <c r="AH2" s="8">
+      <c r="AH2" s="6">
         <v>2027</v>
       </c>
-      <c r="AI2" s="8">
+      <c r="AI2" s="6">
         <v>2027</v>
       </c>
-      <c r="AJ2" s="8">
+      <c r="AJ2" s="6">
         <v>2027</v>
       </c>
-      <c r="AK2" s="8">
+      <c r="AK2" s="6">
         <v>2027</v>
       </c>
-      <c r="AL2" s="8">
+      <c r="AL2" s="6">
         <v>2027</v>
       </c>
-      <c r="AM2" s="8">
+      <c r="AM2" s="6">
         <v>2028</v>
       </c>
-      <c r="AN2" s="8">
+      <c r="AN2" s="6">
         <v>2028</v>
       </c>
-      <c r="AO2" s="8">
+      <c r="AO2" s="6">
         <v>2028</v>
       </c>
-      <c r="AP2" s="8">
+      <c r="AP2" s="6">
         <v>2028</v>
       </c>
-      <c r="AQ2" s="8">
+      <c r="AQ2" s="6">
         <v>2028</v>
       </c>
-      <c r="AR2" s="8">
+      <c r="AR2" s="6">
         <v>2028</v>
       </c>
-      <c r="AS2" s="8">
+      <c r="AS2" s="6">
         <v>2028</v>
       </c>
-      <c r="AT2" s="8">
+      <c r="AT2" s="6">
         <v>2028</v>
       </c>
-      <c r="AU2" s="8">
+      <c r="AU2" s="6">
         <v>2028</v>
       </c>
-      <c r="AV2" s="8">
+      <c r="AV2" s="6">
         <v>2028</v>
       </c>
-      <c r="AW2" s="8">
+      <c r="AW2" s="6">
         <v>2028</v>
       </c>
-      <c r="AX2" s="8">
+      <c r="AX2" s="6">
         <v>2028</v>
       </c>
-      <c r="AY2" s="8">
+      <c r="AY2" s="6">
         <v>2029</v>
       </c>
-      <c r="AZ2" s="8">
+      <c r="AZ2" s="6">
         <v>2029</v>
       </c>
-      <c r="BA2" s="8">
+      <c r="BA2" s="6">
         <v>2029</v>
       </c>
-      <c r="BB2" s="8">
+      <c r="BB2" s="6">
         <v>2029</v>
       </c>
-      <c r="BC2" s="8">
+      <c r="BC2" s="6">
         <v>2029</v>
       </c>
-      <c r="BD2" s="8">
+      <c r="BD2" s="6">
         <v>2029</v>
       </c>
-      <c r="BE2" s="8">
+      <c r="BE2" s="6">
         <v>2029</v>
       </c>
-      <c r="BF2" s="8">
+      <c r="BF2" s="6">
         <v>2029</v>
       </c>
-      <c r="BG2" s="8">
+      <c r="BG2" s="6">
         <v>2029</v>
       </c>
-      <c r="BH2" s="8">
+      <c r="BH2" s="6">
         <v>2029</v>
       </c>
-      <c r="BI2" s="8">
+      <c r="BI2" s="6">
         <v>2029</v>
       </c>
-      <c r="BJ2" s="8">
+      <c r="BJ2" s="6">
         <v>2029</v>
       </c>
     </row>
     <row r="3" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
+      <c r="A3" s="4">
         <v>32</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>55</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <v>58</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>58</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>65</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="5">
         <v>67</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="5">
         <v>68</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="5">
         <v>68</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="5">
         <v>64</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="5">
         <v>64</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="5">
         <v>65</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="5">
         <v>68</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="5">
         <v>68</v>
       </c>
-      <c r="O3" s="7">
-        <v>52</v>
-      </c>
-      <c r="P3" s="7">
+      <c r="O3" s="5">
+        <v>42</v>
+      </c>
+      <c r="P3" s="5">
+        <v>43</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>42</v>
+      </c>
+      <c r="R3" s="5">
+        <v>44</v>
+      </c>
+      <c r="S3" s="5">
+        <v>46</v>
+      </c>
+      <c r="T3" s="5">
+        <v>47</v>
+      </c>
+      <c r="U3" s="5">
+        <v>47</v>
+      </c>
+      <c r="V3" s="5">
+        <v>47</v>
+      </c>
+      <c r="W3" s="5">
+        <v>47</v>
+      </c>
+      <c r="X3" s="5">
+        <v>47</v>
+      </c>
+      <c r="Y3" s="5">
+        <v>47</v>
+      </c>
+      <c r="Z3" s="5">
+        <v>47</v>
+      </c>
+      <c r="AA3" s="5">
+        <v>46</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>47</v>
+      </c>
+      <c r="AC3" s="5">
         <v>55</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="AD3" s="5">
+        <v>62</v>
+      </c>
+      <c r="AE3" s="5">
+        <v>64</v>
+      </c>
+      <c r="AF3" s="5">
+        <v>65</v>
+      </c>
+      <c r="AG3" s="5">
+        <v>63</v>
+      </c>
+      <c r="AH3" s="5">
+        <v>62</v>
+      </c>
+      <c r="AI3" s="5">
+        <v>62</v>
+      </c>
+      <c r="AJ3" s="5">
+        <v>62</v>
+      </c>
+      <c r="AK3" s="5">
+        <v>65</v>
+      </c>
+      <c r="AL3" s="5">
+        <v>65</v>
+      </c>
+      <c r="AM3" s="5">
+        <v>43</v>
+      </c>
+      <c r="AN3" s="5">
+        <v>46</v>
+      </c>
+      <c r="AO3" s="5">
+        <v>46</v>
+      </c>
+      <c r="AP3" s="5">
+        <v>53</v>
+      </c>
+      <c r="AQ3" s="5">
         <v>55</v>
       </c>
-      <c r="R3" s="7">
-        <v>62</v>
-      </c>
-      <c r="S3" s="7">
-        <v>64</v>
-      </c>
-      <c r="T3" s="7">
-        <v>65</v>
-      </c>
-      <c r="U3" s="7">
-        <v>63</v>
-      </c>
-      <c r="V3" s="7">
-        <v>62</v>
-      </c>
-      <c r="W3" s="7">
-        <v>62</v>
-      </c>
-      <c r="X3" s="7">
-        <v>62</v>
-      </c>
-      <c r="Y3" s="7">
-        <v>65</v>
-      </c>
-      <c r="Z3" s="7">
-        <v>65</v>
-      </c>
-      <c r="AA3" s="7">
-        <v>52</v>
-      </c>
-      <c r="AB3" s="7">
-        <v>55</v>
-      </c>
-      <c r="AC3" s="7">
-        <v>55</v>
-      </c>
-      <c r="AD3" s="7">
-        <v>62</v>
-      </c>
-      <c r="AE3" s="7">
-        <v>64</v>
-      </c>
-      <c r="AF3" s="7">
-        <v>65</v>
-      </c>
-      <c r="AG3" s="7">
-        <v>63</v>
-      </c>
-      <c r="AH3" s="7">
-        <v>62</v>
-      </c>
-      <c r="AI3" s="7">
-        <v>62</v>
-      </c>
-      <c r="AJ3" s="7">
-        <v>62</v>
-      </c>
-      <c r="AK3" s="7">
-        <v>65</v>
-      </c>
-      <c r="AL3" s="7">
-        <v>65</v>
-      </c>
-      <c r="AM3" s="7">
-        <v>43</v>
-      </c>
-      <c r="AN3" s="7">
-        <v>46</v>
-      </c>
-      <c r="AO3" s="7">
-        <v>46</v>
-      </c>
-      <c r="AP3" s="7">
+      <c r="AR3" s="5">
+        <v>56</v>
+      </c>
+      <c r="AS3" s="5">
+        <v>54</v>
+      </c>
+      <c r="AT3" s="5">
         <v>53</v>
       </c>
-      <c r="AQ3" s="7">
-        <v>55</v>
-      </c>
-      <c r="AR3" s="7">
+      <c r="AU3" s="5">
+        <v>53</v>
+      </c>
+      <c r="AV3" s="5">
+        <v>53</v>
+      </c>
+      <c r="AW3" s="5">
         <v>56</v>
       </c>
-      <c r="AS3" s="7">
-        <v>54</v>
-      </c>
-      <c r="AT3" s="7">
-        <v>53</v>
-      </c>
-      <c r="AU3" s="7">
-        <v>53</v>
-      </c>
-      <c r="AV3" s="7">
-        <v>53</v>
-      </c>
-      <c r="AW3" s="7">
+      <c r="AX3" s="5">
         <v>56</v>
       </c>
-      <c r="AX3" s="7">
-        <v>56</v>
-      </c>
-      <c r="AY3" s="7">
+      <c r="AY3" s="5">
         <v>38</v>
       </c>
-      <c r="AZ3" s="7">
+      <c r="AZ3" s="5">
         <v>41</v>
       </c>
-      <c r="BA3" s="7">
+      <c r="BA3" s="5">
         <v>41</v>
       </c>
-      <c r="BB3" s="7">
+      <c r="BB3" s="5">
         <v>48</v>
       </c>
-      <c r="BC3" s="7">
+      <c r="BC3" s="5">
         <v>50</v>
       </c>
-      <c r="BD3" s="7">
+      <c r="BD3" s="5">
         <v>51</v>
       </c>
-      <c r="BE3" s="7">
+      <c r="BE3" s="5">
         <v>49</v>
       </c>
-      <c r="BF3" s="7">
+      <c r="BF3" s="5">
         <v>48</v>
       </c>
-      <c r="BG3" s="7">
+      <c r="BG3" s="5">
         <v>48</v>
       </c>
-      <c r="BH3" s="7">
+      <c r="BH3" s="5">
         <v>48</v>
       </c>
-      <c r="BI3" s="7">
+      <c r="BI3" s="5">
         <v>51</v>
       </c>
-      <c r="BJ3" s="7">
+      <c r="BJ3" s="5">
         <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
+      <c r="A4" s="4">
         <v>64</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>69</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>71</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>74</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>71</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <v>89</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="5">
         <v>91</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="5">
         <v>88</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="5">
         <v>88</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="5">
         <v>88</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="5">
         <v>89</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="5">
         <v>88</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="5">
         <v>89</v>
       </c>
-      <c r="O4" s="7">
-        <v>83</v>
-      </c>
-      <c r="P4" s="7">
-        <v>85</v>
-      </c>
-      <c r="Q4" s="7">
+      <c r="O4" s="5">
         <v>88</v>
       </c>
-      <c r="R4" s="7">
+      <c r="P4" s="5">
         <v>88</v>
       </c>
-      <c r="S4" s="7">
-        <v>106</v>
-      </c>
-      <c r="T4" s="7">
-        <v>108</v>
-      </c>
-      <c r="U4" s="7">
-        <v>105</v>
-      </c>
-      <c r="V4" s="7">
-        <v>105</v>
-      </c>
-      <c r="W4" s="7">
-        <v>105</v>
-      </c>
-      <c r="X4" s="7">
-        <v>106</v>
-      </c>
-      <c r="Y4" s="7">
-        <v>92</v>
-      </c>
-      <c r="Z4" s="7">
+      <c r="Q4" s="5">
+        <v>90</v>
+      </c>
+      <c r="R4" s="5">
+        <v>95</v>
+      </c>
+      <c r="S4" s="5">
+        <v>101</v>
+      </c>
+      <c r="T4" s="5">
+        <v>104</v>
+      </c>
+      <c r="U4" s="5">
+        <v>104</v>
+      </c>
+      <c r="V4" s="5">
+        <v>104</v>
+      </c>
+      <c r="W4" s="5">
+        <v>103</v>
+      </c>
+      <c r="X4" s="5">
+        <v>103</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>101</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>101</v>
+      </c>
+      <c r="AA4" s="5">
+        <v>99</v>
+      </c>
+      <c r="AB4" s="5">
+        <v>104</v>
+      </c>
+      <c r="AC4" s="5">
+        <v>90</v>
+      </c>
+      <c r="AD4" s="5">
+        <v>99</v>
+      </c>
+      <c r="AE4" s="5">
+        <v>115</v>
+      </c>
+      <c r="AF4" s="5">
+        <v>117</v>
+      </c>
+      <c r="AG4" s="5">
+        <v>115</v>
+      </c>
+      <c r="AH4" s="5">
+        <v>115</v>
+      </c>
+      <c r="AI4" s="5">
+        <v>115</v>
+      </c>
+      <c r="AJ4" s="5">
+        <v>115</v>
+      </c>
+      <c r="AK4" s="5">
+        <v>103</v>
+      </c>
+      <c r="AL4" s="5">
+        <v>104</v>
+      </c>
+      <c r="AM4" s="5">
         <v>93</v>
       </c>
-      <c r="AA4" s="7">
-        <v>85</v>
-      </c>
-      <c r="AB4" s="7">
-        <v>87</v>
-      </c>
-      <c r="AC4" s="7">
-        <v>90</v>
-      </c>
-      <c r="AD4" s="7">
+      <c r="AN4" s="5">
+        <v>95</v>
+      </c>
+      <c r="AO4" s="5">
+        <v>98</v>
+      </c>
+      <c r="AP4" s="5">
+        <v>107</v>
+      </c>
+      <c r="AQ4" s="5">
+        <v>123</v>
+      </c>
+      <c r="AR4" s="5">
+        <v>125</v>
+      </c>
+      <c r="AS4" s="5">
+        <v>123</v>
+      </c>
+      <c r="AT4" s="5">
+        <v>123</v>
+      </c>
+      <c r="AU4" s="5">
+        <v>123</v>
+      </c>
+      <c r="AV4" s="5">
+        <v>123</v>
+      </c>
+      <c r="AW4" s="5">
+        <v>111</v>
+      </c>
+      <c r="AX4" s="5">
+        <v>112</v>
+      </c>
+      <c r="AY4" s="5">
+        <v>97</v>
+      </c>
+      <c r="AZ4" s="5">
         <v>99</v>
       </c>
-      <c r="AE4" s="7">
+      <c r="BA4" s="5">
+        <v>102</v>
+      </c>
+      <c r="BB4" s="5">
+        <v>111</v>
+      </c>
+      <c r="BC4" s="5">
+        <v>127</v>
+      </c>
+      <c r="BD4" s="5">
+        <v>129</v>
+      </c>
+      <c r="BE4" s="5">
+        <v>127</v>
+      </c>
+      <c r="BF4" s="5">
+        <v>127</v>
+      </c>
+      <c r="BG4" s="5">
+        <v>127</v>
+      </c>
+      <c r="BH4" s="5">
+        <v>127</v>
+      </c>
+      <c r="BI4" s="5">
         <v>115</v>
       </c>
-      <c r="AF4" s="7">
-        <v>117</v>
-      </c>
-      <c r="AG4" s="7">
-        <v>115</v>
-      </c>
-      <c r="AH4" s="7">
-        <v>115</v>
-      </c>
-      <c r="AI4" s="7">
-        <v>115</v>
-      </c>
-      <c r="AJ4" s="7">
-        <v>115</v>
-      </c>
-      <c r="AK4" s="7">
-        <v>103</v>
-      </c>
-      <c r="AL4" s="7">
-        <v>104</v>
-      </c>
-      <c r="AM4" s="7">
-        <v>93</v>
-      </c>
-      <c r="AN4" s="7">
-        <v>95</v>
-      </c>
-      <c r="AO4" s="7">
-        <v>98</v>
-      </c>
-      <c r="AP4" s="7">
-        <v>107</v>
-      </c>
-      <c r="AQ4" s="7">
-        <v>123</v>
-      </c>
-      <c r="AR4" s="7">
-        <v>125</v>
-      </c>
-      <c r="AS4" s="7">
-        <v>123</v>
-      </c>
-      <c r="AT4" s="7">
-        <v>123</v>
-      </c>
-      <c r="AU4" s="7">
-        <v>123</v>
-      </c>
-      <c r="AV4" s="7">
-        <v>123</v>
-      </c>
-      <c r="AW4" s="7">
-        <v>111</v>
-      </c>
-      <c r="AX4" s="7">
-        <v>112</v>
-      </c>
-      <c r="AY4" s="7">
-        <v>97</v>
-      </c>
-      <c r="AZ4" s="7">
-        <v>99</v>
-      </c>
-      <c r="BA4" s="7">
-        <v>102</v>
-      </c>
-      <c r="BB4" s="7">
-        <v>111</v>
-      </c>
-      <c r="BC4" s="7">
-        <v>127</v>
-      </c>
-      <c r="BD4" s="7">
-        <v>129</v>
-      </c>
-      <c r="BE4" s="7">
-        <v>127</v>
-      </c>
-      <c r="BF4" s="7">
-        <v>127</v>
-      </c>
-      <c r="BG4" s="7">
-        <v>127</v>
-      </c>
-      <c r="BH4" s="7">
-        <v>127</v>
-      </c>
-      <c r="BI4" s="7">
-        <v>115</v>
-      </c>
-      <c r="BJ4" s="7">
+      <c r="BJ4" s="5">
         <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:62" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
+      <c r="A5" s="4">
         <v>64</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7">
-        <v>7</v>
-      </c>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
-      <c r="AC5" s="7"/>
-      <c r="AD5" s="7"/>
-      <c r="AE5" s="7"/>
-      <c r="AF5" s="7"/>
-      <c r="AG5" s="7"/>
-      <c r="AH5" s="7"/>
-      <c r="AI5" s="7"/>
-      <c r="AJ5" s="7"/>
-      <c r="AK5" s="7"/>
-      <c r="AL5" s="7"/>
-      <c r="AM5" s="7"/>
-      <c r="AN5" s="7"/>
-      <c r="AO5" s="7"/>
-      <c r="AP5" s="7"/>
-      <c r="AQ5" s="7"/>
-      <c r="AR5" s="7"/>
-      <c r="AS5" s="7"/>
-      <c r="AT5" s="7"/>
-      <c r="AU5" s="7"/>
-      <c r="AV5" s="7"/>
-      <c r="AW5" s="7"/>
-      <c r="AX5" s="7"/>
-      <c r="AY5" s="7"/>
-      <c r="AZ5" s="7"/>
-      <c r="BA5" s="7"/>
-      <c r="BB5" s="7"/>
-      <c r="BC5" s="7"/>
-      <c r="BD5" s="7"/>
-      <c r="BE5" s="7"/>
-      <c r="BF5" s="7"/>
-      <c r="BG5" s="7"/>
-      <c r="BH5" s="7"/>
-      <c r="BI5" s="7"/>
-      <c r="BJ5" s="7"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5">
+        <v>6</v>
+      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="5"/>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="5"/>
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="5"/>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="5"/>
+      <c r="AJ5" s="5"/>
+      <c r="AK5" s="5"/>
+      <c r="AL5" s="5"/>
+      <c r="AM5" s="5"/>
+      <c r="AN5" s="5"/>
+      <c r="AO5" s="5"/>
+      <c r="AP5" s="5"/>
+      <c r="AQ5" s="5"/>
+      <c r="AR5" s="5"/>
+      <c r="AS5" s="5"/>
+      <c r="AT5" s="5"/>
+      <c r="AU5" s="5"/>
+      <c r="AV5" s="5"/>
+      <c r="AW5" s="5"/>
+      <c r="AX5" s="5"/>
+      <c r="AY5" s="5"/>
+      <c r="AZ5" s="5"/>
+      <c r="BA5" s="5"/>
+      <c r="BB5" s="5"/>
+      <c r="BC5" s="5"/>
+      <c r="BD5" s="5"/>
+      <c r="BE5" s="5"/>
+      <c r="BF5" s="5"/>
+      <c r="BG5" s="5"/>
+      <c r="BH5" s="5"/>
+      <c r="BI5" s="5"/>
+      <c r="BJ5" s="5"/>
     </row>
     <row r="6" spans="1:62" x14ac:dyDescent="0.35">
       <c r="A6" t="s">

--- a/data_input/source_data/Program_heli.xlsx
+++ b/data_input/source_data/Program_heli.xlsx
@@ -968,112 +968,112 @@
         <v>47</v>
       </c>
       <c r="AA3" s="5">
+        <v>42</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>43</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>42</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>44</v>
+      </c>
+      <c r="AE3" s="5">
         <v>46</v>
       </c>
-      <c r="AB3" s="5">
-        <v>47</v>
-      </c>
-      <c r="AC3" s="5">
-        <v>55</v>
-      </c>
-      <c r="AD3" s="5">
-        <v>62</v>
-      </c>
-      <c r="AE3" s="5">
-        <v>64</v>
-      </c>
       <c r="AF3" s="5">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="AG3" s="5">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="AH3" s="5">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="AI3" s="5">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="AJ3" s="5">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="AK3" s="5">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="AL3" s="5">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="AM3" s="5">
+        <v>42</v>
+      </c>
+      <c r="AN3" s="5">
         <v>43</v>
       </c>
-      <c r="AN3" s="5">
+      <c r="AO3" s="5">
+        <v>42</v>
+      </c>
+      <c r="AP3" s="5">
+        <v>44</v>
+      </c>
+      <c r="AQ3" s="5">
         <v>46</v>
       </c>
-      <c r="AO3" s="5">
+      <c r="AR3" s="5">
+        <v>47</v>
+      </c>
+      <c r="AS3" s="5">
+        <v>47</v>
+      </c>
+      <c r="AT3" s="5">
+        <v>47</v>
+      </c>
+      <c r="AU3" s="5">
+        <v>47</v>
+      </c>
+      <c r="AV3" s="5">
+        <v>47</v>
+      </c>
+      <c r="AW3" s="5">
+        <v>47</v>
+      </c>
+      <c r="AX3" s="5">
+        <v>47</v>
+      </c>
+      <c r="AY3" s="5">
+        <v>42</v>
+      </c>
+      <c r="AZ3" s="5">
+        <v>43</v>
+      </c>
+      <c r="BA3" s="5">
+        <v>42</v>
+      </c>
+      <c r="BB3" s="5">
+        <v>44</v>
+      </c>
+      <c r="BC3" s="5">
         <v>46</v>
       </c>
-      <c r="AP3" s="5">
-        <v>53</v>
-      </c>
-      <c r="AQ3" s="5">
-        <v>55</v>
-      </c>
-      <c r="AR3" s="5">
-        <v>56</v>
-      </c>
-      <c r="AS3" s="5">
-        <v>54</v>
-      </c>
-      <c r="AT3" s="5">
-        <v>53</v>
-      </c>
-      <c r="AU3" s="5">
-        <v>53</v>
-      </c>
-      <c r="AV3" s="5">
-        <v>53</v>
-      </c>
-      <c r="AW3" s="5">
-        <v>56</v>
-      </c>
-      <c r="AX3" s="5">
-        <v>56</v>
-      </c>
-      <c r="AY3" s="5">
-        <v>38</v>
-      </c>
-      <c r="AZ3" s="5">
-        <v>41</v>
-      </c>
-      <c r="BA3" s="5">
-        <v>41</v>
-      </c>
-      <c r="BB3" s="5">
-        <v>48</v>
-      </c>
-      <c r="BC3" s="5">
-        <v>50</v>
-      </c>
       <c r="BD3" s="5">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="BE3" s="5">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="BF3" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="BG3" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="BH3" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="BI3" s="5">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="BJ3" s="5">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:62" x14ac:dyDescent="0.35">
